--- a/dailyMotivate.xlsx
+++ b/dailyMotivate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wu Jiahao\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wu Jiahao\Desktop\dailyMotivate\dailyMotivate\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>事务</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,10 +35,6 @@
   </si>
   <si>
     <t>英语听写</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200个单词</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -102,6 +98,14 @@
   </si>
   <si>
     <t>Tensorflow学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100个单词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财经系列书籍阅读</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -482,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1618"/>
+  <dimension ref="A1:R1618"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -502,7 +506,7 @@
     <col min="17" max="17" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,150 +514,154 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" t="s">
-        <v>19</v>
-      </c>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>43848</v>
       </c>
       <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>43849</v>
       </c>
       <c r="B4" s="6"/>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>43850</v>
       </c>
+      <c r="B5" s="6"/>
       <c r="J5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P5" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="Q5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>43851</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>43852</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>43853</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>43854</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>43855</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>43856</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>43857</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>43858</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>43859</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>43860</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>43861</v>
       </c>

--- a/dailyMotivate.xlsx
+++ b/dailyMotivate.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>事务</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -108,12 +108,105 @@
     <t>财经系列书籍阅读</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>熟悉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Swift</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语言，熟练掌握</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Xcode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等相关开发工具，熟悉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>iOS SDK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，熟悉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>SQLite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等数据库；</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看书一个小时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,6 +229,19 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -184,7 +290,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -204,6 +310,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -486,27 +595,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R1618"/>
+  <dimension ref="A1:S1618"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.4140625" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="24.9140625" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="8.4140625" customWidth="1"/>
-    <col min="11" max="11" width="31.75" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" customWidth="1"/>
-    <col min="15" max="15" width="17.1640625" customWidth="1"/>
-    <col min="16" max="16" width="36.5" customWidth="1"/>
-    <col min="17" max="17" width="12.6640625" customWidth="1"/>
+    <col min="4" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.4140625" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="24.9140625" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="8.4140625" customWidth="1"/>
+    <col min="12" max="12" width="31.75" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="17.1640625" customWidth="1"/>
+    <col min="17" max="17" width="36.5" customWidth="1"/>
+    <col min="18" max="18" width="12.6640625" customWidth="1"/>
+    <col min="19" max="19" width="16.4140625" customWidth="1"/>
+    <col min="20" max="20" width="44.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -520,23 +631,26 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -550,7 +664,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -564,25 +678,31 @@
       <c r="I2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>43848</v>
       </c>
       <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>43849</v>
       </c>
       <c r="B4" s="6"/>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>43850</v>
       </c>
       <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
       <c r="J5" s="4" t="s">
         <v>14</v>
       </c>
@@ -610,58 +730,64 @@
       <c r="R5" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S5" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>43851</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>43852</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>43853</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>43854</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>43855</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>43856</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>43857</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>43858</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>43859</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>43860</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>43861</v>
       </c>
